--- a/stories/arbres/ATOM-SEC.RUE.002-03.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Inès va à la bibliothèque avec papa. Le sac sent le papier. Ils arrivent au passage. Inès pose les pieds sur le trottoir. Elle donne la main à papa. Papa est l'adulte. Ils restent sur le trottoir en attendant. Papa dit : on attend le feu vert. Inès tient la main. Le feu vert arrive. Papa dit : feu vert. On avance avec l'adulte. Inès marche. Ses pieds suivent papa. La main reste tenue. Ils prennent deux livres. Les pages sentent le bois. Au retour, un autre passage. Inès se souvient. Elle pose les pieds sur le trottoir. Elle donne encore la main. Ils restent sur le trottoir en attendant. Inès dit : on attend le feu vert. Papa dit : oui. Avec l'adulte. Le feu vert arrive. Ils avancent ensemble. La main reste tenue. Inès est fière.</t>
+          <t>Inès va à la bibliothèque avec papa. Le sac sent le papier. Ils arrivent au passage. Inès pose les pieds sur le trottoir. Elle donne la main à papa. Papa est l'adulte. Ils restent sur le trottoir en attendant. On attend le feu vert. Inès tient la main. Le feu vert arrive. Feu vert. On avance avec l'adulte. Inès marche. Ses pieds suivent papa. La main reste tenue. Ils prennent deux livres. Les pages sentent le bois. Au retour, un autre passage. Inès se souvient. Elle pose les pieds sur le trottoir. Elle donne encore la main. Ils restent sur le trottoir en attendant. On attend le feu vert. Oui. Avec l'adulte. Le feu vert arrive. Ils avancent ensemble. La main reste tenue. Inès est fière.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Inès va à la bibliothèque avec papa. Le sac sent le papier. Ils arrivent au passage. Inès pose les pieds sur le trottoir. Elle donne la main à papa. Papa est l'adulte. Ils restent sur le trottoir en attendant.
+papa|On attend le feu vert.
+narrateur|Inès tient la main. Le feu vert arrive.
+papa|Feu vert. On avance avec l'adulte.
+narrateur|Inès marche. Ses pieds suivent papa. La main reste tenue. Ils prennent deux livres. Les pages sentent le bois. Au retour, un autre passage. Inès se souvient. Elle pose les pieds sur le trottoir. Elle donne encore la main. Ils restent sur le trottoir en attendant.
+enfant-f|On attend le feu vert.
+papa|Oui. Avec l'adulte.
+narrateur|Le feu vert arrive. Ils avancent ensemble. La main reste tenue. Inès est fière.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1497,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Inès est au passage. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1674,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a attendu le feu vert. La main était tenue. L'adulte guidait. Elle a repris le geste au retour.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1803,6 +1841,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Inès porte les deux livres. Papa ouvre la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1965,6 +2008,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1983,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2000,6 +2048,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.002-03.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 narrateur|Le feu vert arrive. Ils avancent ensemble. La main reste tenue. Inès est fière.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1504,6 +1510,7 @@
           <t>narrateur|Inès est au passage. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1679,6 +1686,7 @@
           <t>narrateur|Inès a attendu le feu vert. La main était tenue. L'adulte guidait. Elle a repris le geste au retour.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1846,6 +1854,7 @@
           <t>narrateur|Inès porte les deux livres. Papa ouvre la porte.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2013,6 +2022,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2031,7 +2041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2055,6 +2065,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2256,6 +2280,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.RUE.002-03.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Inès attend le feu vert deux fois</t>
+          <t>Le châtaignier d'Amir</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le châtaignier jette des ombres. Amir veut montrer une châtaigne à l'école. Deux rues. La châtaigne roule. Il serre la main, attend le vert deux fois.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Inès va à la bibliothèque avec papa. Le sac sent le papier. Ils arrivent au passage. Inès pose les pieds sur le trottoir. Elle donne la main à papa. Papa est l'adulte. Ils restent sur le trottoir en attendant. On attend le feu vert. Inès tient la main. Le feu vert arrive. Feu vert. On avance avec l'adulte. Inès marche. Ses pieds suivent papa. La main reste tenue. Ils prennent deux livres. Les pages sentent le bois. Au retour, un autre passage. Inès se souvient. Elle pose les pieds sur le trottoir. Elle donne encore la main. Ils restent sur le trottoir en attendant. On attend le feu vert. Oui. Avec l'adulte. Le feu vert arrive. Ils avancent ensemble. La main reste tenue. Inès est fière.</t>
+          <t>Le châtaignier jette des ombres longues. Une bogue éclatée brille dans l'herbe. L'air sent la feuille mouillée et le bois. Amir glisse une châtaigne lisse dans sa poche. Elle est froide, un peu luisante. Le cartable tape sa hanche, tout rythmé. Tu as pris ta châtaigne, Amir ? Oui, papa. Je la montre à l'école. Elle est belle. En ce moment, Amir donne la main. La main de papa est chaude, un peu rêche. On marche sur le trottoir. Ils passent sous les branches basses. Une feuille tourne, puis se pose. Elle tourne ! Oui. Le premier passage arrive près du kiosque. On s'arrête. Tu serres ma main ? Amir serre la main. Ses pieds restent sur le trottoir. Le petit bonhomme est rouge. On attend le vert. Un camion passe, tout lent. Il fait du vent. On attend ensemble. Puis le petit bonhomme devient vert. Feu vert. On avance ensemble. Ils avancent avec papa, sans se lâcher. Le cartable se balance encore. Une deuxième rue coupe le chemin de l'école. La châtaigne glisse de la poche. Elle roule vers la bordure. Ma châtaigne ! On reste sur le trottoir. Tu serres ma main ? Amir serre plus fort. Il pose les pieds au bord, et il attend. La châtaigne s'arrête contre une racine, sur le trottoir. Le petit bonhomme est encore rouge. On attend le vert. Merci, Amir. J'attends. Le portail de l'école brille, un peu plus loin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Inès va à la bibliothèque avec papa. Le sac sent le papier. Ils arrivent au passage. Inès pose les pieds sur le trottoir. Elle donne la main à papa. Papa est l'adulte. Ils restent sur le trottoir en attendant. Papa dit : on attend le &lt;emphasis level="moderate"&gt;feu&lt;/emphasis&gt; vert. Inès tient la main. Le feu vert arrive. Papa dit : feu vert. On avance avec l'adulte. Inès marche. Ses pieds suivent papa. La main reste tenue. Ils prennent deux livres. Les pages sentent le bois. Au retour, un autre passage. Inès se souvient. Elle pose les pieds sur le trottoir. Elle donne encore la main. Ils restent sur le trottoir en attendant. Inès dit : on attend le feu vert. Papa dit : oui. Avec l'adulte. Le feu vert arrive. Ils avancent ensemble. La main reste tenue. Inès est fière.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le châtaignier jette des ombres longues. Une bogue éclatée brille dans l'herbe. L'air sent la feuille mouillée et le bois. Amir glisse une châtaigne lisse dans sa poche. Elle est froide, un peu luisante. Le cartable tape sa hanche, tout rythmé. Tu as pris ta châtaigne, Amir ? Oui, papa. Je la montre à l'école. Elle est belle. En ce moment, Amir donne la main. La main de papa est chaude, un peu rêche. On marche sur le trottoir. Ils passent sous les branches basses. Une feuille tourne, puis se pose. Elle tourne ! Oui. Le premier passage arrive près du kiosque. On s'arrête. Tu serres ma main ? Amir serre la main. Ses pieds restent sur le trottoir. Le petit bonhomme est rouge. On attend le vert. Un camion passe, tout lent. Il fait du vent. On attend ensemble. Puis le petit bonhomme devient vert. Feu vert. On avance ensemble. Ils avancent avec papa, sans se lâcher. Le cartable se balance encore. Une deuxième rue coupe le chemin de l'école. La châtaigne glisse de la poche. Elle roule vers la bordure. Ma châtaigne ! On reste sur le trottoir. Tu serres ma main ? Amir serre plus fort. Il pose les pieds au bord, et il attend. La châtaigne s'arrête contre une racine, sur le trottoir. Le petit bonhomme est encore rouge. On attend le vert. Merci, Amir. J'attends. Le portail de l'école brille, un peu plus loin.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,17 +1324,59 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Inès va à la bibliothèque avec papa. Le sac sent le papier. Ils arrivent au passage. Inès pose les pieds sur le trottoir. Elle donne la main à papa. Papa est l'adulte. Ils restent sur le trottoir en attendant.
-papa|On attend le feu vert.
-narrateur|Inès tient la main. Le feu vert arrive.
-papa|Feu vert. On avance avec l'adulte.
-narrateur|Inès marche. Ses pieds suivent papa. La main reste tenue. Ils prennent deux livres. Les pages sentent le bois. Au retour, un autre passage. Inès se souvient. Elle pose les pieds sur le trottoir. Elle donne encore la main. Ils restent sur le trottoir en attendant.
-enfant-f|On attend le feu vert.
-papa|Oui. Avec l'adulte.
-narrateur|Le feu vert arrive. Ils avancent ensemble. La main reste tenue. Inès est fière.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le châtaignier jette des ombres longues.
+narrateur|Une bogue éclatée brille dans l'herbe.
+narrateur|L'air sent la feuille mouillée et le bois.
+narrateur|Amir glisse une châtaigne lisse dans sa poche.
+narrateur|Elle est froide, un peu luisante.
+narrateur|Le cartable tape sa hanche, tout rythmé.
+papa|Tu as pris ta châtaigne, Amir ?
+enfant-m|Oui, papa.
+enfant-m|Je la montre à l'école.
+papa|Elle est belle.
+narrateur|En ce moment, Amir donne la main.
+narrateur|La main de papa est chaude, un peu rêche.
+papa|On marche sur le trottoir.
+narrateur|Ils passent sous les branches basses.
+narrateur|Une feuille tourne, puis se pose.
+enfant-m|Elle tourne !
+papa|Oui.
+narrateur|Le premier passage arrive près du kiosque.
+papa|On s'arrête.
+papa|Tu serres ma main ?
+narrateur|Amir serre la main.
+narrateur|Ses pieds restent sur le trottoir.
+narrateur|Le petit bonhomme est rouge.
+papa|On attend le vert.
+narrateur|Un camion passe, tout lent.
+enfant-m|Il fait du vent.
+papa|On attend ensemble.
+narrateur|Puis le petit bonhomme devient vert.
+papa|Feu vert.
+papa|On avance ensemble.
+narrateur|Ils avancent avec papa, sans se lâcher.
+narrateur|Le cartable se balance encore.
+narrateur|Une deuxième rue coupe le chemin de l'école.
+narrateur|La châtaigne glisse de la poche.
+narrateur|Elle roule vers la bordure.
+enfant-m|Ma châtaigne !
+papa|On reste sur le trottoir.
+papa|Tu serres ma main ?
+narrateur|Amir serre plus fort.
+narrateur|Il pose les pieds au bord, et il attend.
+narrateur|La châtaigne s'arrête contre une racine, sur le trottoir.
+narrateur|Le petit bonhomme est encore rouge.
+papa|On attend le vert.
+papa|Merci, Amir.
+enfant-m|J'attends.
+narrateur|Le portail de l'école brille, un peu plus loin.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>voiture_passe</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1347,12 +1401,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Inès est au passage. Que fait-elle ?</t>
+          <t>Amir est au passage, avec papa. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Inès est au passage. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir est au passage, avec papa. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1367,7 +1421,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>feu vert | la main | avec papa | avec l'adulte | attendre</t>
+          <t>feu vert | la main | avec maman | avec papa | avec l'adulte | attendre | le vert</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1382,7 +1436,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle attend le feu vert. Elle donne la main. Que fait Inès ?</t>
+          <t>Il serre la main. Il attend le feu vert. Que fait Amir ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1431,7 +1485,7 @@
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1507,10 +1561,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Inès est au passage. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Amir est au passage, avec papa.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1535,12 +1589,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Inès a attendu le feu vert. La main était tenue. L'adulte guidait. Elle a repris le geste au retour.</t>
+          <t>Amir a serré la main. Il a attendu le feu vert. Ses pieds restaient sur le trottoir. Tu as attendu le vert ? Oui, papa. La châtaigne brille encore contre la racine. Le cartable sent le crayon et le bois.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Inès a attendu le &lt;emphasis level="moderate"&gt;feu&lt;/emphasis&gt; vert. La main était tenue. L'adulte guidait. Elle a repris le geste au retour.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a serré la main. Il a attendu le feu vert. Ses pieds restaient sur le trottoir. Tu as attendu le vert ? Oui, papa. La châtaigne brille encore contre la racine. Le cartable sent le crayon et le bois.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1596,7 +1650,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
@@ -1683,10 +1737,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Inès a attendu le feu vert. La main était tenue. L'adulte guidait. Elle a repris le geste au retour.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Amir a serré la main.
+narrateur|Il a attendu le feu vert.
+narrateur|Ses pieds restaient sur le trottoir.
+papa|Tu as attendu le vert ?
+enfant-m|Oui, papa.
+narrateur|La châtaigne brille encore contre la racine.
+narrateur|Le cartable sent le crayon et le bois.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1711,12 +1770,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Inès porte les deux livres. Papa ouvre la porte.</t>
+          <t>Le petit bonhomme devient vert. Feu vert. On avance ensemble. Amir ramasse la châtaigne, sur le trottoir. Elle est froide, toute lisse. Elle est à moi. Tu la remets dans la poche ? Oui. Ils avancent avec papa jusqu'au portail. La cour sent les feuilles et la craie. Je la montre. Oui. Une cloche d'école tinte, toute claire.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Inès porte les deux livres. Papa ouvre la porte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le petit bonhomme devient vert. Feu vert. On avance ensemble. Amir ramasse la châtaigne, sur le trottoir. Elle est froide, toute lisse. Elle est à moi. Tu la remets dans la poche ? Oui. Ils avancent avec papa jusqu'au portail. La cour sent les feuilles et la craie. Je la montre. Oui. Une cloche d'école tinte, toute claire.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1772,7 +1831,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
@@ -1851,10 +1910,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Inès porte les deux livres. Papa ouvre la porte.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le petit bonhomme devient vert.
+papa|Feu vert.
+papa|On avance ensemble.
+narrateur|Amir ramasse la châtaigne, sur le trottoir.
+narrateur|Elle est froide, toute lisse.
+enfant-m|Elle est à moi.
+papa|Tu la remets dans la poche ?
+enfant-m|Oui.
+narrateur|Ils avancent avec papa jusqu'au portail.
+narrateur|La cour sent les feuilles et la craie.
+enfant-m|Je la montre.
+papa|Oui.
+narrateur|Une cloche d'école tinte, toute claire.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1879,12 +1949,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir touche la châtaigne dans sa poche. Elle tiédit un peu contre le tissu. Elle est chaude maintenant. Oui. Une châtaigne tiède reste dans la poche.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir touche la châtaigne dans sa poche. Elle tiédit un peu contre le tissu. Elle est chaude maintenant. Oui. Une châtaigne tiède reste dans la poche.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1940,7 +2010,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
@@ -2019,10 +2089,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Amir touche la châtaigne dans sa poche.
+narrateur|Elle tiédit un peu contre le tissu.
+enfant-m|Elle est chaude maintenant.
+papa|Oui.
+narrateur|Une châtaigne tiède reste dans la poche.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2041,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2079,6 +2152,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.002-03.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>trajet vers la bibliothèque</t>
+          <t>chemin sous le châtaignier vers l'école</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Inès, papa</t>
+          <t>Amir, papa</t>
         </is>
       </c>
     </row>
